--- a/backend/uploads/敏感信息脱敏测试数据-正式.xlsx
+++ b/backend/uploads/敏感信息脱敏测试数据-正式.xlsx
@@ -25015,7 +25015,7 @@
   <dimension ref="A1:F1344"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="56.4247787610619" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.4690265486726" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.4513274336283" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.6548672566372" style="1" customWidth="1"/>
     <col min="4" max="4" width="23.4513274336283" style="1" customWidth="1"/>
